--- a/RFP_Brief_ First on SoundCloud 2021 Campaign - Scenarios A & B - Workfront Export.xlsx
+++ b/RFP_Brief_ First on SoundCloud 2021 Campaign - Scenarios A & B - Workfront Export.xlsx
@@ -56,11 +56,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O112"/>
+  <dimension ref="A1:R112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,42 +469,57 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Service Department</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Seniority</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Planned_Hours</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Start_Offset_Days</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Duration_Days</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Assignee_External_ID</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Rate_USD</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Price_USD</t>
         </is>
       </c>
     </row>
@@ -533,13 +550,24 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -571,21 +599,28 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" s="2" t="n">
         <v>227</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Core/T2_MediumVolume</t>
         </is>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>44265</v>
       </c>
     </row>
     <row r="4">
@@ -622,22 +657,29 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>9750</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -675,32 +717,39 @@
           <t>Accessibility Audit</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Accessibility Specialist</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -738,32 +787,39 @@
           <t>Accessibility QA</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>1.1.1.1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -801,32 +857,39 @@
           <t>Code Review</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Frontend Engineer</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>1.1.1.2</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>8580</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -862,22 +925,29 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -915,32 +985,39 @@
           <t>Analytics Audit</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Business Analyst</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -976,22 +1053,29 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1029,32 +1113,39 @@
           <t>Documentation</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Business Analyst</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>1.1.3</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1090,22 +1181,29 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>1.1.3</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>8385</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1143,32 +1241,39 @@
           <t>Design Consult</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>UI Designer</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>1.1.4</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1206,32 +1311,39 @@
           <t>Accessibility QA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>1.1.4.1</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>1170</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1269,32 +1381,39 @@
           <t>Code Review</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Backend Engineer</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>1.1.4.2</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>6630</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1330,22 +1449,29 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>1.1.4</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>8385</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1383,32 +1509,39 @@
           <t>Design Consult</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>UI Designer</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>1.1.5</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1446,32 +1579,39 @@
           <t>Accessibility QA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>1.1.5.1</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>1170</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1509,32 +1649,39 @@
           <t>Code Review</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Backend Engineer</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>1.1.5.2</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>6630</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1570,22 +1717,29 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>1.1.5</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1623,32 +1777,39 @@
           <t>QA Cycle</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>1.1.6</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1686,32 +1847,39 @@
           <t>Define &amp; Configure Goals</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>1.1.6.1</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1747,22 +1915,29 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>1.1.6</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1800,32 +1975,39 @@
           <t>QA Cycle</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>1.1.7</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1863,32 +2045,39 @@
           <t>Event Schema &amp; Tagging</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>1.1.7.1</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1924,22 +2113,29 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>1.1.7</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1977,32 +2173,39 @@
           <t>Spec QA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>1.1.8</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2040,32 +2243,39 @@
           <t>Pixel Setup (GTM)</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>1.1.8.1</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2101,22 +2311,29 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>1.1.8</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2154,32 +2371,39 @@
           <t>QA Cycle</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>1.1.9</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2217,32 +2441,39 @@
           <t>Migrate UA Goals → GA4 Conversions</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>1.1.9.1</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2278,22 +2509,29 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>1.1.9</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2331,32 +2569,39 @@
           <t>QA Cycle</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>1.1.10</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2394,32 +2639,39 @@
           <t>Implement Tags/Events</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>1.1.10.1</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2455,22 +2707,29 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>1.1.10</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2508,32 +2767,39 @@
           <t>QA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>1.1.11</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2571,32 +2837,39 @@
           <t>Event Config</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>1.1.11.1</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2632,22 +2905,29 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>1.1.11</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2685,32 +2965,39 @@
           <t>Publish &amp; Smoke Test</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>1.1.12</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2746,22 +3033,29 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>1.1.12</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2799,32 +3093,39 @@
           <t>QA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>1.1.13</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2862,32 +3163,39 @@
           <t>Cross-domain Config</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>1.1.13.1</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2923,22 +3231,29 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>1.1.13</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2976,32 +3291,39 @@
           <t>QA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>1.1.14</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3039,32 +3361,39 @@
           <t>Ecommerce Data Layer</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>1.1.14.1</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3100,22 +3429,29 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="n">
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>1.1.14</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3153,32 +3489,39 @@
           <t>QA Cycle</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>1.1.15</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3216,32 +3559,39 @@
           <t>GA4 Property Setup</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>1.1.15.1</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3273,25 +3623,32 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="n">
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
         <is>
           <t>Core/T2_MediumVolume</t>
         </is>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>36660</v>
       </c>
     </row>
     <row r="50">
@@ -3328,22 +3685,29 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="n">
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3381,32 +3745,39 @@
           <t>Rights/License Research</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>1.2.1</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3444,32 +3815,39 @@
           <t>Usage Notes</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>1.2.1.1</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3505,22 +3883,29 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="n">
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>1.2.1</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3558,32 +3943,39 @@
           <t>Script Polish</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
         <is>
           <t>Copywriter</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3621,32 +4013,39 @@
           <t>VO Session</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
         <is>
           <t>Sound Designer</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>1.2.2.1</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3682,22 +4081,29 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="n">
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3735,32 +4141,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>1.2.3</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3796,22 +4209,29 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="n">
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>1.2.3</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>4875</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3849,32 +4269,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>1.2.4</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>4875</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3910,22 +4337,29 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="n">
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>1.2.4</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3963,32 +4397,39 @@
           <t>VO Edit</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>1.2.5</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>1755</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4026,32 +4467,39 @@
           <t>Mix</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
         <is>
           <t>Sound Designer</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>1.2.5.1</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4089,32 +4537,39 @@
           <t>Internal Review &amp; Critique</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>1.2.5.2</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4152,32 +4607,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>1.2.5.3</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4215,32 +4677,39 @@
           <t>Final Packaging</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
         <is>
           <t>Designer</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="L65" t="n">
+      <c r="M65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>1.2.5.4</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4276,22 +4745,29 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="n">
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>1.2.5</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4329,32 +4805,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="L67" t="n">
+      <c r="M67" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>1.2.6</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4390,22 +4873,29 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="n">
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="L68" t="n">
+      <c r="M68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>1.2.6</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>2145</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4443,32 +4933,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
         <is>
           <t>Colorist</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="L69" t="n">
+      <c r="M69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>1.2.7</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>2145</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4504,22 +5001,29 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="n">
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="L70" t="n">
+      <c r="M70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>1.2.7</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>2145</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4557,32 +5061,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
         <is>
           <t>Colorist</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="L71" t="n">
+      <c r="M71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>1.2.8</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>2145</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4618,22 +5129,29 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="n">
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>1.2.8</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>1950</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4671,32 +5189,39 @@
           <t>Retouch</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
         <is>
           <t>Retoucher</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>1.2.9</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4734,32 +5259,39 @@
           <t>Internal Review &amp; Critique</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="K74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K74" t="n">
+      <c r="L74" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="L74" t="n">
+      <c r="M74" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>1.2.9.1</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4797,32 +5329,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>1.2.9.2</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4860,32 +5399,39 @@
           <t>Final Packaging</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
         <is>
           <t>Designer</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J76" t="n">
+      <c r="K76" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K76" t="n">
+      <c r="L76" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="L76" t="n">
+      <c r="M76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>1.2.9.3</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4921,22 +5467,29 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="n">
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>1.2.9</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>1950</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4974,32 +5527,39 @@
           <t>Retouch</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
         <is>
           <t>Retoucher</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J78" t="n">
+      <c r="K78" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="L78" t="n">
+      <c r="M78" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>1.2.10</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5037,32 +5597,39 @@
           <t>Internal Review &amp; Critique</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="K79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>1.2.10.1</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5100,32 +5667,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J80" t="n">
+      <c r="K80" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K80" t="n">
+      <c r="L80" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L80" t="n">
+      <c r="M80" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>1.2.10.2</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5163,32 +5737,39 @@
           <t>Final Packaging</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
         <is>
           <t>Designer</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>1.2.10.3</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5224,22 +5805,29 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="n">
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K82" t="n">
+      <c r="L82" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="L82" t="n">
+      <c r="M82" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>1.2.10</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>1755</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5277,32 +5865,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
         <is>
           <t>Designer</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="L83" t="n">
+      <c r="M83" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>1.2.11</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>1755</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5338,22 +5933,29 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="n">
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K84" t="n">
+      <c r="L84" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="L84" t="n">
+      <c r="M84" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>1.2.11</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5391,32 +5993,39 @@
           <t>Music Search &amp; License</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
         <is>
           <t>Sound Designer</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J85" t="n">
+      <c r="K85" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K85" t="n">
+      <c r="L85" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="L85" t="n">
+      <c r="M85" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>1.2.12</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5452,22 +6061,29 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="n">
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>1.2.12</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5505,32 +6121,39 @@
           <t>QA (Tech &amp; Content)</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
         <is>
           <t>QA Specialist</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J87" t="n">
+      <c r="K87" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K87" t="n">
+      <c r="L87" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="L87" t="n">
+      <c r="M87" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>1.2.13</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5568,32 +6191,39 @@
           <t>Final Checklist &amp; Upload</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
         <is>
           <t>Media Manager / DIT</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="K88" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K88" t="n">
+      <c r="L88" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="L88" t="n">
+      <c r="M88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>1.2.13.1</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5629,22 +6259,29 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="n">
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K89" t="n">
+      <c r="L89" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="L89" t="n">
+      <c r="M89" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>1.2.13</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>1950</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5682,32 +6319,39 @@
           <t>Change Orders &amp; Tracking</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J90" t="n">
+      <c r="K90" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="L90" t="n">
+      <c r="M90" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>1.2.14</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R90" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5745,32 +6389,39 @@
           <t>Internal Review &amp; Critique</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J91" t="n">
+      <c r="K91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="L91" t="n">
+      <c r="M91" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>1.2.14.1</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5808,32 +6459,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J92" t="n">
+      <c r="K92" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K92" t="n">
+      <c r="L92" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>1.2.14.2</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5871,32 +6529,39 @@
           <t>Invoice Reconciliation</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
         <is>
           <t>Designer</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J93" t="n">
+      <c r="K93" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K93" t="n">
+      <c r="L93" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="L93" t="n">
+      <c r="M93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>1.2.14.3</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5932,22 +6597,29 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="n">
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K94" t="n">
+      <c r="L94" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="L94" t="n">
+      <c r="M94" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>1.2.14</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R94" s="2" t="n">
+        <v>2145</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5985,32 +6657,39 @@
           <t>Internal Review &amp; Critique</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J95" t="n">
+      <c r="K95" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K95" t="n">
+      <c r="L95" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="L95" t="n">
+      <c r="M95" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>1.2.15</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6048,32 +6727,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J96" t="n">
+      <c r="K96" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K96" t="n">
+      <c r="L96" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L96" t="n">
+      <c r="M96" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>1.2.15.1</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R96" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6111,32 +6797,39 @@
           <t>Cutdowns (2-3)</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J97" t="n">
+      <c r="K97" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K97" t="n">
+      <c r="L97" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="L97" t="n">
+      <c r="M97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>1.2.15.2</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6172,22 +6865,29 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="n">
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K98" t="n">
+      <c r="L98" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L98" t="n">
+      <c r="M98" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>1.2.15</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6225,32 +6925,39 @@
           <t>Client Review Coordination</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J99" t="n">
+      <c r="K99" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K99" t="n">
+      <c r="L99" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L99" t="n">
+      <c r="M99" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>1.2.16</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6286,22 +6993,29 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="n">
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K100" t="n">
+      <c r="L100" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L100" t="n">
+      <c r="M100" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>1.2.16</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6339,32 +7053,39 @@
           <t>Client Review Coordination</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J101" t="n">
+      <c r="K101" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K101" t="n">
+      <c r="L101" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L101" t="n">
+      <c r="M101" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>1.2.17</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6402,32 +7123,39 @@
           <t>Notes Triage</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J102" t="n">
+      <c r="K102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K102" t="n">
+      <c r="L102" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="L102" t="n">
+      <c r="M102" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t>1.2.17.1</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6463,22 +7191,29 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="n">
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K103" t="n">
+      <c r="L103" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="L103" t="n">
+      <c r="M103" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>1.2.17</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6516,32 +7251,39 @@
           <t>Post Support</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J104" t="n">
+      <c r="K104" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K104" t="n">
+      <c r="L104" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="L104" t="n">
+      <c r="M104" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t>1.2.18</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6577,22 +7319,29 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="n">
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K105" t="n">
+      <c r="L105" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="L105" t="n">
+      <c r="M105" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="N105" t="inlineStr">
         <is>
           <t>1.2.18</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6630,32 +7379,39 @@
           <t>Post Support</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J106" t="n">
+      <c r="K106" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K106" t="n">
+      <c r="L106" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="L106" t="n">
+      <c r="M106" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M106" t="inlineStr">
+      <c r="N106" t="inlineStr">
         <is>
           <t>1.2.19</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R106" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6691,22 +7447,29 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="n">
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K107" t="n">
+      <c r="L107" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="L107" t="n">
+      <c r="M107" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M107" t="inlineStr">
+      <c r="N107" t="inlineStr">
         <is>
           <t>1.2.19</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R107" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6744,32 +7507,39 @@
           <t>Post Support</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J108" t="n">
+      <c r="K108" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K108" t="n">
+      <c r="L108" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="L108" t="n">
+      <c r="M108" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M108" t="inlineStr">
+      <c r="N108" t="inlineStr">
         <is>
           <t>1.2.20</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6805,22 +7575,29 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="n">
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K109" t="n">
+      <c r="L109" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="L109" t="n">
+      <c r="M109" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M109" t="inlineStr">
+      <c r="N109" t="inlineStr">
         <is>
           <t>1.2.20</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R109" s="2" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6858,32 +7635,39 @@
           <t>Post Support</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J110" t="n">
+      <c r="K110" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K110" t="n">
+      <c r="L110" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="L110" t="n">
+      <c r="M110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M110" t="inlineStr">
+      <c r="N110" t="inlineStr">
         <is>
           <t>1.2.21</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6919,22 +7703,29 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="n">
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K111" t="n">
+      <c r="L111" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="L111" t="n">
+      <c r="M111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M111" t="inlineStr">
+      <c r="N111" t="inlineStr">
         <is>
           <t>1.2.21</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R111" s="2" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6972,32 +7763,39 @@
           <t>Post Support</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J112" t="n">
+      <c r="K112" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K112" t="n">
+      <c r="L112" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="L112" t="n">
+      <c r="M112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M112" t="inlineStr">
+      <c r="N112" t="inlineStr">
         <is>
           <t>1.2.22</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R112" s="2" t="n">
+        <v>975</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7010,7 +7808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O112"/>
+  <dimension ref="A1:R112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7051,42 +7849,57 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Service Department</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Seniority</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Planned_Hours</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Start_Offset_Days</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Duration_Days</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Assignee_External_ID</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Rate_USD</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Price_USD</t>
         </is>
       </c>
     </row>
@@ -7117,13 +7930,24 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7155,21 +7979,28 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" s="2" t="n">
         <v>348</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Advanced/T1_LargeVolume</t>
         </is>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>67860</v>
       </c>
     </row>
     <row r="4">
@@ -7206,22 +8037,29 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>15015</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7259,32 +8097,39 @@
           <t>Accessibility Audit</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Accessibility Specialist</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7322,32 +8167,39 @@
           <t>Accessibility QA</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>1.1.1.1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>1170</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7385,32 +8237,39 @@
           <t>Code Review</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Frontend Engineer</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>1.1.1.2</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>13260</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7446,22 +8305,29 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>5070</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7499,32 +8365,39 @@
           <t>Analytics Audit</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Business Analyst</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>5070</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7560,22 +8433,29 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>5070</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7613,32 +8493,39 @@
           <t>Documentation</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Business Analyst</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>1.1.3</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>5070</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7674,22 +8561,29 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>1.1.3</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>12870</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7727,32 +8621,39 @@
           <t>Design Consult</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>UI Designer</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>1.1.4</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7790,32 +8691,39 @@
           <t>Accessibility QA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>1.1.4.1</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>1755</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7853,32 +8761,39 @@
           <t>Code Review</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Backend Engineer</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>1.1.4.2</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>10140</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7914,22 +8829,29 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>1.1.4</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>12870</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7967,32 +8889,39 @@
           <t>Design Consult</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>UI Designer</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>1.1.5</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8030,32 +8959,39 @@
           <t>Accessibility QA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>1.1.5.1</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>1755</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8093,32 +9029,39 @@
           <t>Code Review</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Backend Engineer</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>1.1.5.2</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>10140</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8154,22 +9097,29 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>1.1.5</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>2145</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8207,32 +9157,39 @@
           <t>QA Cycle</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>1.1.6</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8270,32 +9227,39 @@
           <t>Define &amp; Configure Goals</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>1.1.6.1</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8331,22 +9295,29 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>1.1.6</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>2145</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8384,32 +9355,39 @@
           <t>QA Cycle</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>1.1.7</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8447,32 +9425,39 @@
           <t>Event Schema &amp; Tagging</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>1.1.7.1</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8508,22 +9493,29 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>1.1.7</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8561,32 +9553,39 @@
           <t>Spec QA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>1.1.8</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8624,32 +9623,39 @@
           <t>Pixel Setup (GTM)</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>1.1.8.1</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8685,22 +9691,29 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>1.1.8</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>1950</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8738,32 +9751,39 @@
           <t>QA Cycle</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>1.1.9</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8801,32 +9821,39 @@
           <t>Migrate UA Goals → GA4 Conversions</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>1.1.9.1</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>1170</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8862,22 +9889,29 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>1.1.9</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>1950</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8915,32 +9949,39 @@
           <t>QA Cycle</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>1.1.10</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8978,32 +10019,39 @@
           <t>Implement Tags/Events</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>1.1.10.1</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>1170</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9039,22 +10087,29 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>1.1.10</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9092,32 +10147,39 @@
           <t>QA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>1.1.11</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9155,32 +10217,39 @@
           <t>Event Config</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>1.1.11.1</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9216,22 +10285,29 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>1.1.11</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9269,32 +10345,39 @@
           <t>Publish &amp; Smoke Test</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>1.1.12</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9330,22 +10413,29 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>1.1.12</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9383,32 +10473,39 @@
           <t>QA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>1.1.13</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9446,32 +10543,39 @@
           <t>Cross-domain Config</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>1.1.13.1</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9507,22 +10611,29 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>1.1.13</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9560,32 +10671,39 @@
           <t>QA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>1.1.14</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9623,32 +10741,39 @@
           <t>Ecommerce Data Layer</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>1.1.14.1</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9684,22 +10809,29 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="n">
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>1.1.14</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>1950</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9737,32 +10869,39 @@
           <t>QA Cycle</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>1.1.15</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9800,32 +10939,39 @@
           <t>GA4 Property Setup</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
         <is>
           <t>Data/Analytics Engineer</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>1.1.15.1</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>1170</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9857,25 +11003,32 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="n">
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" s="2" t="n">
         <v>288</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
         <is>
           <t>Advanced/T1_LargeVolume</t>
         </is>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>56160</v>
       </c>
     </row>
     <row r="50">
@@ -9912,22 +11065,29 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="n">
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9965,32 +11125,39 @@
           <t>Rights/License Research</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>1.2.1</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -10028,32 +11195,39 @@
           <t>Usage Notes</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>1.2.1.1</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -10089,22 +11263,29 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="n">
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>1.2.1</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -10142,32 +11323,39 @@
           <t>Script Polish</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
         <is>
           <t>Copywriter</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -10205,32 +11393,39 @@
           <t>VO Session</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
         <is>
           <t>Sound Designer</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>1.2.2.1</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -10266,22 +11461,29 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="n">
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>5070</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -10319,32 +11521,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>1.2.3</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>5070</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -10380,22 +11589,29 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="n">
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>1.2.3</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>7605</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -10433,32 +11649,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>1.2.4</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>7605</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -10494,22 +11717,29 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="n">
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>1.2.4</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>5070</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -10547,32 +11777,39 @@
           <t>VO Edit</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>1.2.5</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>2535</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -10610,32 +11847,39 @@
           <t>Mix</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
         <is>
           <t>Sound Designer</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>1.2.5.1</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10673,32 +11917,39 @@
           <t>Internal Review &amp; Critique</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>1.2.5.2</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10736,32 +11987,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>1.2.5.3</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10799,32 +12057,39 @@
           <t>Final Packaging</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
         <is>
           <t>Designer</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="L65" t="n">
+      <c r="M65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>1.2.5.4</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10860,22 +12125,29 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="n">
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>1.2.5</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>5070</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10913,32 +12185,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="L67" t="n">
+      <c r="M67" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>1.2.6</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>5070</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10974,22 +12253,29 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="n">
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="L68" t="n">
+      <c r="M68" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>1.2.6</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -11027,32 +12313,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
         <is>
           <t>Colorist</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="L69" t="n">
+      <c r="M69" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>1.2.7</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -11088,22 +12381,29 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="n">
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="L70" t="n">
+      <c r="M70" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>1.2.7</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -11141,32 +12441,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
         <is>
           <t>Colorist</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="L71" t="n">
+      <c r="M71" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>1.2.8</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -11202,22 +12509,29 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="n">
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>1.2.8</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>3120</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -11255,32 +12569,39 @@
           <t>Retouch</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
         <is>
           <t>Retoucher</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>1.2.9</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -11318,32 +12639,39 @@
           <t>Internal Review &amp; Critique</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="K74" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K74" t="n">
+      <c r="L74" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="L74" t="n">
+      <c r="M74" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>1.2.9.1</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -11381,32 +12709,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>1.2.9.2</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -11444,32 +12779,39 @@
           <t>Final Packaging</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
         <is>
           <t>Designer</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J76" t="n">
+      <c r="K76" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K76" t="n">
+      <c r="L76" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="L76" t="n">
+      <c r="M76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>1.2.9.3</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -11505,22 +12847,29 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="n">
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>1.2.9</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>3120</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -11558,32 +12907,39 @@
           <t>Retouch</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
         <is>
           <t>Retoucher</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J78" t="n">
+      <c r="K78" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L78" t="n">
+      <c r="M78" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>1.2.10</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -11621,32 +12977,39 @@
           <t>Internal Review &amp; Critique</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="K79" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>1.2.10.1</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -11684,32 +13047,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J80" t="n">
+      <c r="K80" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K80" t="n">
+      <c r="L80" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="L80" t="n">
+      <c r="M80" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>1.2.10.2</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -11747,32 +13117,39 @@
           <t>Final Packaging</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
         <is>
           <t>Designer</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>1.2.10.3</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -11808,22 +13185,29 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="n">
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K82" t="n">
+      <c r="L82" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="L82" t="n">
+      <c r="M82" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>1.2.10</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>2535</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -11861,32 +13245,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
         <is>
           <t>Designer</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="L83" t="n">
+      <c r="M83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>1.2.11</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>2535</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -11922,22 +13313,29 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="n">
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K84" t="n">
+      <c r="L84" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="L84" t="n">
+      <c r="M84" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>1.2.11</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -11975,32 +13373,39 @@
           <t>Music Search &amp; License</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
         <is>
           <t>Sound Designer</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J85" t="n">
+      <c r="K85" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K85" t="n">
+      <c r="L85" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="L85" t="n">
+      <c r="M85" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>1.2.12</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -12036,22 +13441,29 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="n">
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>1.2.12</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>1950</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -12089,32 +13501,39 @@
           <t>QA (Tech &amp; Content)</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
         <is>
           <t>QA Specialist</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J87" t="n">
+      <c r="K87" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K87" t="n">
+      <c r="L87" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="L87" t="n">
+      <c r="M87" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>1.2.13</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -12152,32 +13571,39 @@
           <t>Final Checklist &amp; Upload</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
         <is>
           <t>Media Manager / DIT</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="K88" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K88" t="n">
+      <c r="L88" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="L88" t="n">
+      <c r="M88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>1.2.13.1</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>1170</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -12213,22 +13639,29 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="n">
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="K89" t="n">
+      <c r="L89" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="L89" t="n">
+      <c r="M89" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>1.2.13</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>2925</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -12266,32 +13699,39 @@
           <t>Change Orders &amp; Tracking</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J90" t="n">
+      <c r="K90" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="L90" t="n">
+      <c r="M90" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>1.2.14</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R90" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -12329,32 +13769,39 @@
           <t>Internal Review &amp; Critique</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J91" t="n">
+      <c r="K91" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="L91" t="n">
+      <c r="M91" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>1.2.14.1</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -12392,32 +13839,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J92" t="n">
+      <c r="K92" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K92" t="n">
+      <c r="L92" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>1.2.14.2</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -12455,32 +13909,39 @@
           <t>Invoice Reconciliation</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
         <is>
           <t>Designer</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J93" t="n">
+      <c r="K93" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K93" t="n">
+      <c r="L93" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="L93" t="n">
+      <c r="M93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>1.2.14.3</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>1365</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -12516,22 +13977,29 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="n">
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K94" t="n">
+      <c r="L94" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="L94" t="n">
+      <c r="M94" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>1.2.14</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R94" s="2" t="n">
+        <v>3315</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12569,32 +14037,39 @@
           <t>Internal Review &amp; Critique</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J95" t="n">
+      <c r="K95" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K95" t="n">
+      <c r="L95" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="L95" t="n">
+      <c r="M95" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>1.2.15</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -12632,32 +14107,39 @@
           <t>Client Review &amp; Revisions</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J96" t="n">
+      <c r="K96" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K96" t="n">
+      <c r="L96" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="L96" t="n">
+      <c r="M96" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>1.2.15.1</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R96" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12695,32 +14177,39 @@
           <t>Cutdowns (2-3)</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J97" t="n">
+      <c r="K97" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K97" t="n">
+      <c r="L97" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="L97" t="n">
+      <c r="M97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>1.2.15.2</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>2145</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12756,22 +14245,29 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="n">
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K98" t="n">
+      <c r="L98" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="L98" t="n">
+      <c r="M98" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>1.2.15</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>1170</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12809,32 +14305,39 @@
           <t>Client Review Coordination</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J99" t="n">
+      <c r="K99" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K99" t="n">
+      <c r="L99" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="L99" t="n">
+      <c r="M99" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>1.2.16</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>1170</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12870,22 +14373,29 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="n">
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K100" t="n">
+      <c r="L100" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="L100" t="n">
+      <c r="M100" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>1.2.16</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12923,32 +14433,39 @@
           <t>Client Review Coordination</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
         <is>
           <t>Account Manager</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J101" t="n">
+      <c r="K101" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K101" t="n">
+      <c r="L101" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="L101" t="n">
+      <c r="M101" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>1.2.17</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12986,32 +14503,39 @@
           <t>Notes Triage</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J102" t="n">
+      <c r="K102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K102" t="n">
+      <c r="L102" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="L102" t="n">
+      <c r="M102" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t>1.2.17.1</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -13047,22 +14571,29 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="n">
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K103" t="n">
+      <c r="L103" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="L103" t="n">
+      <c r="M103" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>1.2.17</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -13100,32 +14631,39 @@
           <t>Post Support</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J104" t="n">
+      <c r="K104" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K104" t="n">
+      <c r="L104" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="L104" t="n">
+      <c r="M104" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t>1.2.18</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13161,22 +14699,29 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="n">
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K105" t="n">
+      <c r="L105" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="L105" t="n">
+      <c r="M105" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="N105" t="inlineStr">
         <is>
           <t>1.2.18</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13214,32 +14759,39 @@
           <t>Post Support</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J106" t="n">
+      <c r="K106" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K106" t="n">
+      <c r="L106" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="L106" t="n">
+      <c r="M106" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M106" t="inlineStr">
+      <c r="N106" t="inlineStr">
         <is>
           <t>1.2.19</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R106" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13275,22 +14827,29 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="n">
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K107" t="n">
+      <c r="L107" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="L107" t="n">
+      <c r="M107" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M107" t="inlineStr">
+      <c r="N107" t="inlineStr">
         <is>
           <t>1.2.19</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R107" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -13328,32 +14887,39 @@
           <t>Post Support</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J108" t="n">
+      <c r="K108" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K108" t="n">
+      <c r="L108" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="L108" t="n">
+      <c r="M108" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M108" t="inlineStr">
+      <c r="N108" t="inlineStr">
         <is>
           <t>1.2.20</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -13389,22 +14955,29 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="n">
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K109" t="n">
+      <c r="L109" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="L109" t="n">
+      <c r="M109" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M109" t="inlineStr">
+      <c r="N109" t="inlineStr">
         <is>
           <t>1.2.20</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R109" s="2" t="n">
+        <v>1560</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -13442,32 +15015,39 @@
           <t>Post Support</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J110" t="n">
+      <c r="K110" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K110" t="n">
+      <c r="L110" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="L110" t="n">
+      <c r="M110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M110" t="inlineStr">
+      <c r="N110" t="inlineStr">
         <is>
           <t>1.2.21</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>1560</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13503,22 +15083,29 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="n">
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K111" t="n">
+      <c r="L111" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="L111" t="n">
+      <c r="M111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M111" t="inlineStr">
+      <c r="N111" t="inlineStr">
         <is>
           <t>1.2.21</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R111" s="2" t="n">
+        <v>1560</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13556,32 +15143,39 @@
           <t>Post Support</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="J112" t="n">
+      <c r="K112" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K112" t="n">
+      <c r="L112" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="L112" t="n">
+      <c r="M112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M112" t="inlineStr">
+      <c r="N112" t="inlineStr">
         <is>
           <t>1.2.22</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R112" s="2" t="n">
+        <v>1560</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
